--- a/data_raw/Term_SOFR_latest.xlsx
+++ b/data_raw/Term_SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E616"/>
+  <dimension ref="A1:E621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12140,6 +12140,101 @@
         <v>0.04472139999999999</v>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>0.0391411</v>
+      </c>
+      <c r="C617" t="n">
+        <v>0.0401795</v>
+      </c>
+      <c r="D617" t="n">
+        <v>0.0416768</v>
+      </c>
+      <c r="E617" t="n">
+        <v>0.04453380000000001</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>0.0391868</v>
+      </c>
+      <c r="C618" t="n">
+        <v>0.0402999</v>
+      </c>
+      <c r="D618" t="n">
+        <v>0.0419095</v>
+      </c>
+      <c r="E618" t="n">
+        <v>0.04495619999999999</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.0391666</v>
+      </c>
+      <c r="C619" t="n">
+        <v>0.0402975</v>
+      </c>
+      <c r="D619" t="n">
+        <v>0.0418252</v>
+      </c>
+      <c r="E619" t="n">
+        <v>0.0447606</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.0392327</v>
+      </c>
+      <c r="C620" t="n">
+        <v>0.04036559999999999</v>
+      </c>
+      <c r="D620" t="n">
+        <v>0.0418994</v>
+      </c>
+      <c r="E620" t="n">
+        <v>0.04472139999999999</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.039249</v>
+      </c>
+      <c r="C621" t="n">
+        <v>0.0403887</v>
+      </c>
+      <c r="D621" t="n">
+        <v>0.0419271</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0.0447215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/Term_SOFR_latest.xlsx
+++ b/data_raw/Term_SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E621"/>
+  <dimension ref="A1:E626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12235,6 +12235,101 @@
         <v>0.0447215</v>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.0392327</v>
+      </c>
+      <c r="C622" t="n">
+        <v>0.04036559999999999</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0.0418994</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0.04472139999999999</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>0.039249</v>
+      </c>
+      <c r="C623" t="n">
+        <v>0.0403887</v>
+      </c>
+      <c r="D623" t="n">
+        <v>0.0419271</v>
+      </c>
+      <c r="E623" t="n">
+        <v>0.0447215</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>0.0392465</v>
+      </c>
+      <c r="C624" t="n">
+        <v>0.0404249</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0.042014</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0.0448795</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.039326</v>
+      </c>
+      <c r="C625" t="n">
+        <v>0.0406116</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0.0421711</v>
+      </c>
+      <c r="E625" t="n">
+        <v>0.0450556</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.0397183</v>
+      </c>
+      <c r="C626" t="n">
+        <v>0.0411624</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0.0429534</v>
+      </c>
+      <c r="E626" t="n">
+        <v>0.04594280000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/Term_SOFR_latest.xlsx
+++ b/data_raw/Term_SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E626"/>
+  <dimension ref="A1:E631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12330,6 +12330,101 @@
         <v>0.04594280000000001</v>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.0392465</v>
+      </c>
+      <c r="C627" t="n">
+        <v>0.0404249</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0.042014</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0.0448795</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.039326</v>
+      </c>
+      <c r="C628" t="n">
+        <v>0.0406116</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0.0421711</v>
+      </c>
+      <c r="E628" t="n">
+        <v>0.0450556</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>0.0397183</v>
+      </c>
+      <c r="C629" t="n">
+        <v>0.0411624</v>
+      </c>
+      <c r="D629" t="n">
+        <v>0.0429534</v>
+      </c>
+      <c r="E629" t="n">
+        <v>0.04594280000000001</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>0.0395082</v>
+      </c>
+      <c r="C630" t="n">
+        <v>0.0408444</v>
+      </c>
+      <c r="D630" t="n">
+        <v>0.0424041</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0.0449607</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.039298</v>
+      </c>
+      <c r="C631" t="n">
+        <v>0.04057330000000001</v>
+      </c>
+      <c r="D631" t="n">
+        <v>0.0421572</v>
+      </c>
+      <c r="E631" t="n">
+        <v>0.0448351</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/Term_SOFR_latest.xlsx
+++ b/data_raw/Term_SOFR_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E631"/>
+  <dimension ref="A1:E636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12425,6 +12425,101 @@
         <v>0.0448351</v>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>0.03924850000000001</v>
+      </c>
+      <c r="C632" t="n">
+        <v>0.0404544</v>
+      </c>
+      <c r="D632" t="n">
+        <v>0.0418483</v>
+      </c>
+      <c r="E632" t="n">
+        <v>0.04427660000000001</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.0393253</v>
+      </c>
+      <c r="C633" t="n">
+        <v>0.0405521</v>
+      </c>
+      <c r="D633" t="n">
+        <v>0.0418967</v>
+      </c>
+      <c r="E633" t="n">
+        <v>0.0442612</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.0393279</v>
+      </c>
+      <c r="C634" t="n">
+        <v>0.0406289</v>
+      </c>
+      <c r="D634" t="n">
+        <v>0.0420576</v>
+      </c>
+      <c r="E634" t="n">
+        <v>0.0445648</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.03929870000000001</v>
+      </c>
+      <c r="C635" t="n">
+        <v>0.0406202</v>
+      </c>
+      <c r="D635" t="n">
+        <v>0.04215790000000001</v>
+      </c>
+      <c r="E635" t="n">
+        <v>0.044776</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>0.0391403</v>
+      </c>
+      <c r="C636" t="n">
+        <v>0.04065940000000001</v>
+      </c>
+      <c r="D636" t="n">
+        <v>0.0422271</v>
+      </c>
+      <c r="E636" t="n">
+        <v>0.0449189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
